--- a/Methanol/Patagonien_Methanol_2_DAC_Brownfield/Datenbank.xlsx
+++ b/Methanol/Patagonien_Methanol_2_DAC_Brownfield/Datenbank.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hem38994\Documents\GitHub\FENES_P2X\Methanol\Methanol_DAC_Brownfield_Patagonien\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hem38994\Documents\GitHub\FENES_P2X\Methanol\Patagonien_Methanol_2_DAC_Brownfield\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{371816FB-1623-48DB-911E-127914C7CED2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92C32D6E-746F-45E7-AC1F-508B9F9693C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-57720" yWindow="-6885" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
     <sheet name="Ergebnisse" sheetId="5" r:id="rId2"/>
     <sheet name="Quelle DAC" sheetId="6" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029" iterate="1" iterateDelta="9.8999999999999999E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -198,7 +198,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="373">
   <si>
     <t>PEM Elektrolyse</t>
   </si>
@@ -1313,6 +1313,12 @@
   </si>
   <si>
     <t>kg</t>
+  </si>
+  <si>
+    <t>Landesspezifischer Zinssatz</t>
+  </si>
+  <si>
+    <t>wacc_change</t>
   </si>
 </sst>
 </file>
@@ -2062,24 +2068,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G72"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G73"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.88671875" style="10" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" style="26" customWidth="1"/>
-    <col min="3" max="3" width="36.21875" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.90625" style="10" customWidth="1"/>
+    <col min="2" max="2" width="18.6328125" style="26" customWidth="1"/>
+    <col min="3" max="3" width="36.1796875" style="10" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21" style="10" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19" style="15" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="40.77734375" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.77734375" style="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.77734375" style="10" customWidth="1"/>
-    <col min="9" max="9" width="13.88671875" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="40.81640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.81640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.81640625" style="10" customWidth="1"/>
+    <col min="9" max="9" width="13.90625" style="10" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14" style="10" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.77734375" style="10" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.88671875" style="10"/>
+    <col min="11" max="11" width="10.81640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.90625" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="7" t="s">
         <v>69</v>
       </c>
@@ -2100,7 +2106,7 @@
       </c>
       <c r="G1" s="26"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="35" t="s">
         <v>70</v>
       </c>
@@ -2120,7 +2126,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="36"/>
       <c r="B3" s="43"/>
       <c r="C3" s="10" t="s">
@@ -2136,7 +2142,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="36"/>
       <c r="B4" s="43"/>
       <c r="C4" s="10" t="s">
@@ -2152,7 +2158,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="36"/>
       <c r="B5" s="43"/>
       <c r="C5" s="10" t="s">
@@ -2168,7 +2174,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="36"/>
       <c r="B6" s="43"/>
       <c r="C6" s="10" t="s">
@@ -2184,7 +2190,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="36"/>
       <c r="B7" s="43"/>
       <c r="C7" s="10" t="s">
@@ -2200,7 +2206,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="36"/>
       <c r="B8" s="46" t="s">
         <v>228</v>
@@ -2218,7 +2224,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="36"/>
       <c r="B9" s="43"/>
       <c r="C9" s="10" t="s">
@@ -2234,7 +2240,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="36"/>
       <c r="B10" s="43"/>
       <c r="C10" s="10" t="s">
@@ -2250,7 +2256,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="36"/>
       <c r="B11" s="43"/>
       <c r="C11" s="10" t="s">
@@ -2266,7 +2272,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="36"/>
       <c r="B12" s="43"/>
       <c r="C12" s="10" t="s">
@@ -2282,7 +2288,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="36"/>
       <c r="B13" s="43"/>
       <c r="C13" s="10" t="s">
@@ -2298,7 +2304,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="36"/>
       <c r="B14" s="43"/>
       <c r="C14" s="10" t="s">
@@ -2314,7 +2320,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="36"/>
       <c r="B15" s="47"/>
       <c r="C15" s="18" t="s">
@@ -2330,7 +2336,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="36"/>
       <c r="B16" s="46" t="s">
         <v>293</v>
@@ -2348,7 +2354,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="36"/>
       <c r="B17" s="43"/>
       <c r="C17" s="10" t="s">
@@ -2364,7 +2370,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="36"/>
       <c r="B18" s="43"/>
       <c r="C18" s="10" t="s">
@@ -2380,7 +2386,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="36"/>
       <c r="B19" s="43"/>
       <c r="C19" s="10" t="s">
@@ -2396,7 +2402,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="36"/>
       <c r="B20" s="43"/>
       <c r="C20" s="10" t="s">
@@ -2412,7 +2418,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="36"/>
       <c r="B21" s="47"/>
       <c r="C21" s="18" t="s">
@@ -2428,7 +2434,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="36"/>
       <c r="B22" s="39" t="s">
         <v>227</v>
@@ -2446,7 +2452,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="36"/>
       <c r="B23" s="39"/>
       <c r="C23" s="10" t="s">
@@ -2462,7 +2468,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="36"/>
       <c r="B24" s="39"/>
       <c r="C24" s="10" t="s">
@@ -2478,7 +2484,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="36"/>
       <c r="B25" s="39"/>
       <c r="C25" s="10" t="s">
@@ -2494,7 +2500,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="36"/>
       <c r="B26" s="39"/>
       <c r="C26" s="10" t="s">
@@ -2510,7 +2516,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A27" s="36"/>
       <c r="B27" s="39"/>
       <c r="C27" s="10" t="s">
@@ -2526,7 +2532,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="35" t="s">
         <v>71</v>
       </c>
@@ -2546,7 +2552,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="36"/>
       <c r="B29" s="39"/>
       <c r="C29" s="10" t="s">
@@ -2562,7 +2568,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="36"/>
       <c r="B30" s="39"/>
       <c r="C30" s="10" t="s">
@@ -2578,7 +2584,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="36"/>
       <c r="B31" s="39"/>
       <c r="C31" s="10" t="s">
@@ -2594,7 +2600,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="36"/>
       <c r="B32" s="39"/>
       <c r="C32" s="10" t="s">
@@ -2610,7 +2616,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="36"/>
       <c r="B33" s="39"/>
       <c r="C33" s="10" t="s">
@@ -2626,7 +2632,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="36"/>
       <c r="B34" s="39"/>
       <c r="C34" s="10" t="s">
@@ -2642,7 +2648,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A35" s="36"/>
       <c r="B35" s="40"/>
       <c r="C35" s="18" t="s">
@@ -2658,7 +2664,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="36"/>
       <c r="B36" s="41" t="s">
         <v>338</v>
@@ -2676,7 +2682,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" s="36"/>
       <c r="B37" s="39"/>
       <c r="C37" s="10" t="s">
@@ -2692,7 +2698,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="36"/>
       <c r="B38" s="39"/>
       <c r="C38" s="10" t="s">
@@ -2708,7 +2714,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" s="36"/>
       <c r="B39" s="39"/>
       <c r="C39" s="10" t="s">
@@ -2724,7 +2730,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="36"/>
       <c r="B40" s="39"/>
       <c r="C40" s="10" t="s">
@@ -2740,7 +2746,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="36"/>
       <c r="B41" s="39"/>
       <c r="C41" s="10" t="s">
@@ -2756,7 +2762,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" s="36"/>
       <c r="B42" s="39"/>
       <c r="C42" s="10" t="s">
@@ -2772,7 +2778,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" s="36"/>
       <c r="B43" s="39"/>
       <c r="C43" s="18" t="s">
@@ -2788,7 +2794,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" s="36"/>
       <c r="B44" s="41" t="s">
         <v>201</v>
@@ -2806,7 +2812,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" s="36"/>
       <c r="B45" s="43"/>
       <c r="C45" s="10" t="s">
@@ -2823,7 +2829,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" s="36"/>
       <c r="B46" s="43"/>
       <c r="C46" s="10" t="s">
@@ -2839,7 +2845,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" s="36"/>
       <c r="B47" s="43"/>
       <c r="C47" s="10" t="s">
@@ -2855,7 +2861,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" s="36"/>
       <c r="B48" s="43"/>
       <c r="C48" s="10" t="s">
@@ -2871,7 +2877,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" s="36"/>
       <c r="B49" s="43"/>
       <c r="C49" s="10" t="s">
@@ -2887,7 +2893,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="36"/>
       <c r="B50" s="43"/>
       <c r="C50" s="10" t="s">
@@ -2903,7 +2909,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="36"/>
       <c r="B51" s="43"/>
       <c r="C51" s="10" t="s">
@@ -2919,7 +2925,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="36"/>
       <c r="B52" s="43"/>
       <c r="C52" s="10" t="s">
@@ -2935,7 +2941,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A53" s="37"/>
       <c r="B53" s="44"/>
       <c r="C53" s="22" t="s">
@@ -2951,7 +2957,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" s="35" t="s">
         <v>72</v>
       </c>
@@ -2971,7 +2977,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" s="36"/>
       <c r="B55" s="41" t="s">
         <v>4</v>
@@ -2989,7 +2995,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" s="36"/>
       <c r="B56" s="39"/>
       <c r="C56" s="10" t="s">
@@ -3005,7 +3011,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" s="36"/>
       <c r="B57" s="39"/>
       <c r="C57" s="10" t="s">
@@ -3021,7 +3027,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" s="36"/>
       <c r="B58" s="39"/>
       <c r="C58" s="10" t="s">
@@ -3037,7 +3043,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" s="36"/>
       <c r="B59" s="39"/>
       <c r="C59" s="10" t="s">
@@ -3053,7 +3059,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" s="36"/>
       <c r="B60" s="39"/>
       <c r="C60" s="10" t="s">
@@ -3069,7 +3075,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" s="36"/>
       <c r="B61" s="40"/>
       <c r="C61" s="18" t="s">
@@ -3085,7 +3091,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" s="36"/>
       <c r="B62" s="41" t="s">
         <v>5</v>
@@ -3103,7 +3109,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" s="36"/>
       <c r="B63" s="39"/>
       <c r="C63" s="10" t="s">
@@ -3119,7 +3125,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" s="36"/>
       <c r="B64" s="39"/>
       <c r="C64" s="10" t="s">
@@ -3135,7 +3141,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" s="36"/>
       <c r="B65" s="39"/>
       <c r="C65" s="10" t="s">
@@ -3151,7 +3157,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" s="36"/>
       <c r="B66" s="39"/>
       <c r="C66" s="10" t="s">
@@ -3167,7 +3173,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" s="36"/>
       <c r="B67" s="39"/>
       <c r="C67" s="10" t="s">
@@ -3183,7 +3189,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" s="37"/>
       <c r="B68" s="42"/>
       <c r="C68" s="22" t="s">
@@ -3199,7 +3205,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" s="35" t="s">
         <v>76</v>
       </c>
@@ -3219,7 +3225,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" s="36"/>
       <c r="B70" s="26" t="s">
         <v>322</v>
@@ -3237,7 +3243,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" s="36"/>
       <c r="B71" s="32" t="s">
         <v>79</v>
@@ -3255,7 +3261,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A72" s="37"/>
       <c r="B72" s="8" t="s">
         <v>272</v>
@@ -3271,6 +3277,26 @@
       </c>
       <c r="F72" s="22" t="s">
         <v>295</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A73" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B73" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C73" s="10" t="s">
+        <v>371</v>
+      </c>
+      <c r="D73" s="10" t="s">
+        <v>372</v>
+      </c>
+      <c r="E73" s="15">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="F73" s="10" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -3298,18 +3324,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83AB2E79-6F94-41B5-A552-C40EC4890194}">
   <dimension ref="A1:F142"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.5546875" style="10" customWidth="1"/>
-    <col min="2" max="2" width="30.33203125" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.5546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="50.77734375" style="10" customWidth="1"/>
-    <col min="5" max="5" width="46.109375" style="10" customWidth="1"/>
-    <col min="6" max="6" width="37.5546875" style="10" customWidth="1"/>
-    <col min="7" max="16384" width="11.5546875" style="10"/>
+    <col min="1" max="1" width="14.54296875" style="10" customWidth="1"/>
+    <col min="2" max="2" width="30.36328125" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.54296875" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="50.81640625" style="10" customWidth="1"/>
+    <col min="5" max="5" width="46.08984375" style="10" customWidth="1"/>
+    <col min="6" max="6" width="37.54296875" style="10" customWidth="1"/>
+    <col min="7" max="16384" width="11.54296875" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="7" t="s">
         <v>69</v>
       </c>
@@ -3329,7 +3355,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="35" t="s">
         <v>70</v>
       </c>
@@ -3347,7 +3373,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="36"/>
       <c r="B3" s="43"/>
       <c r="C3" s="10" t="s">
@@ -3361,7 +3387,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="36"/>
       <c r="B4" s="43"/>
       <c r="C4" s="10" t="s">
@@ -3375,7 +3401,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="36"/>
       <c r="B5" s="43"/>
       <c r="C5" s="10" t="s">
@@ -3389,7 +3415,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="36"/>
       <c r="B6" s="43"/>
       <c r="C6" s="10" t="s">
@@ -3403,7 +3429,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="36"/>
       <c r="B7" s="43"/>
       <c r="C7" s="10" t="s">
@@ -3417,7 +3443,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="36"/>
       <c r="B8" s="43"/>
       <c r="C8" s="10" t="s">
@@ -3431,7 +3457,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="36"/>
       <c r="B9" s="43"/>
       <c r="C9" s="10" t="s">
@@ -3445,7 +3471,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="36"/>
       <c r="B10" s="43"/>
       <c r="C10" s="10" t="s">
@@ -3459,12 +3485,12 @@
         <v>149</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="36"/>
       <c r="B11" s="43"/>
       <c r="E11" s="15"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="36"/>
       <c r="B12" s="46" t="s">
         <v>228</v>
@@ -3480,7 +3506,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="36"/>
       <c r="B13" s="43"/>
       <c r="C13" s="10" t="s">
@@ -3494,7 +3520,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="36"/>
       <c r="B14" s="43"/>
       <c r="C14" s="10" t="s">
@@ -3508,7 +3534,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="36"/>
       <c r="B15" s="43"/>
       <c r="C15" s="10" t="s">
@@ -3522,7 +3548,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="36"/>
       <c r="B16" s="43"/>
       <c r="C16" s="10" t="s">
@@ -3536,7 +3562,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="36"/>
       <c r="B17" s="43"/>
       <c r="C17" s="10" t="s">
@@ -3550,7 +3576,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="36"/>
       <c r="B18" s="43"/>
       <c r="C18" s="10" t="s">
@@ -3564,7 +3590,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="36"/>
       <c r="B19" s="43"/>
       <c r="C19" s="10" t="s">
@@ -3578,7 +3604,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="36"/>
       <c r="B20" s="43"/>
       <c r="C20" s="10" t="s">
@@ -3592,7 +3618,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="36"/>
       <c r="B21" s="43"/>
       <c r="C21" s="10" t="s">
@@ -3606,7 +3632,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="36"/>
       <c r="B22" s="47"/>
       <c r="C22" s="18"/>
@@ -3614,7 +3640,7 @@
       <c r="E22" s="19"/>
       <c r="F22" s="18"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="36"/>
       <c r="B23" s="46" t="s">
         <v>293</v>
@@ -3630,7 +3656,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="36"/>
       <c r="B24" s="43"/>
       <c r="C24" s="10" t="s">
@@ -3644,7 +3670,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="36"/>
       <c r="B25" s="43"/>
       <c r="C25" s="10" t="s">
@@ -3658,7 +3684,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="36"/>
       <c r="B26" s="43"/>
       <c r="C26" s="10" t="s">
@@ -3672,7 +3698,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="36"/>
       <c r="B27" s="43"/>
       <c r="C27" s="10" t="s">
@@ -3686,7 +3712,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="36"/>
       <c r="B28" s="43"/>
       <c r="C28" s="10" t="s">
@@ -3700,7 +3726,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="36"/>
       <c r="B29" s="43"/>
       <c r="C29" s="10" t="s">
@@ -3714,7 +3740,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="36"/>
       <c r="B30" s="43"/>
       <c r="C30" s="10" t="s">
@@ -3728,7 +3754,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="36"/>
       <c r="B31" s="43"/>
       <c r="C31" s="10" t="s">
@@ -3742,7 +3768,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="36"/>
       <c r="B32" s="47"/>
       <c r="C32" s="18"/>
@@ -3750,7 +3776,7 @@
       <c r="E32" s="19"/>
       <c r="F32" s="18"/>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="36"/>
       <c r="B33" s="39" t="s">
         <v>227</v>
@@ -3766,7 +3792,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="36"/>
       <c r="B34" s="39"/>
       <c r="C34" s="10" t="s">
@@ -3780,7 +3806,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="36"/>
       <c r="B35" s="39"/>
       <c r="C35" s="10" t="s">
@@ -3794,7 +3820,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="36"/>
       <c r="B36" s="39"/>
       <c r="C36" s="10" t="s">
@@ -3808,7 +3834,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" s="36"/>
       <c r="B37" s="39"/>
       <c r="C37" s="10" t="s">
@@ -3822,7 +3848,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="36"/>
       <c r="B38" s="39"/>
       <c r="C38" s="10" t="s">
@@ -3836,7 +3862,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" s="36"/>
       <c r="B39" s="39"/>
       <c r="C39" s="10" t="s">
@@ -3850,7 +3876,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="36"/>
       <c r="B40" s="39"/>
       <c r="C40" s="10" t="s">
@@ -3864,7 +3890,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="36"/>
       <c r="B41" s="39"/>
       <c r="C41" s="10" t="s">
@@ -3878,7 +3904,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" s="36"/>
       <c r="B42" s="39"/>
       <c r="C42" s="10" t="s">
@@ -3892,12 +3918,12 @@
         <v>149</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A43" s="36"/>
       <c r="B43" s="39"/>
       <c r="E43" s="15"/>
     </row>
-    <row r="44" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="35" t="s">
         <v>71</v>
       </c>
@@ -3915,7 +3941,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" s="36"/>
       <c r="B45" s="39"/>
       <c r="C45" s="10" t="s">
@@ -3929,7 +3955,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" s="36"/>
       <c r="B46" s="39"/>
       <c r="C46" s="10" t="s">
@@ -3943,7 +3969,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" s="36"/>
       <c r="B47" s="39"/>
       <c r="C47" s="10" t="s">
@@ -3957,7 +3983,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" s="36"/>
       <c r="B48" s="39"/>
       <c r="C48" s="10" t="s">
@@ -3971,7 +3997,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" s="36"/>
       <c r="B49" s="39"/>
       <c r="C49" s="10" t="s">
@@ -3985,7 +4011,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="36"/>
       <c r="B50" s="39"/>
       <c r="C50" s="10" t="s">
@@ -3999,7 +4025,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="36"/>
       <c r="B51" s="39"/>
       <c r="C51" s="10" t="s">
@@ -4013,7 +4039,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="36"/>
       <c r="B52" s="39"/>
       <c r="C52" s="10" t="s">
@@ -4027,7 +4053,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" s="36"/>
       <c r="B53" s="40"/>
       <c r="C53" s="18"/>
@@ -4035,7 +4061,7 @@
       <c r="E53" s="19"/>
       <c r="F53" s="18"/>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" s="36"/>
       <c r="B54" s="39" t="s">
         <v>338</v>
@@ -4051,7 +4077,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" s="36"/>
       <c r="B55" s="39"/>
       <c r="C55" s="10" t="s">
@@ -4065,7 +4091,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" s="36"/>
       <c r="B56" s="39"/>
       <c r="C56" s="10" t="s">
@@ -4079,7 +4105,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" s="36"/>
       <c r="B57" s="39"/>
       <c r="C57" s="10" t="s">
@@ -4093,7 +4119,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" s="36"/>
       <c r="B58" s="39"/>
       <c r="C58" s="10" t="s">
@@ -4107,7 +4133,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" s="36"/>
       <c r="B59" s="39"/>
       <c r="C59" s="10" t="s">
@@ -4121,7 +4147,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" s="36"/>
       <c r="B60" s="39"/>
       <c r="C60" s="10" t="s">
@@ -4135,7 +4161,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" s="36"/>
       <c r="B61" s="39"/>
       <c r="C61" s="10" t="s">
@@ -4149,7 +4175,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" s="36"/>
       <c r="B62" s="39"/>
       <c r="C62" s="10" t="s">
@@ -4163,12 +4189,12 @@
         <v>149</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" s="36"/>
       <c r="B63" s="40"/>
       <c r="E63" s="15"/>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" s="36"/>
       <c r="B64" s="41" t="s">
         <v>6</v>
@@ -4184,7 +4210,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" s="36"/>
       <c r="B65" s="39"/>
       <c r="C65" s="10" t="s">
@@ -4198,7 +4224,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" s="36"/>
       <c r="B66" s="43"/>
       <c r="C66" s="10" t="s">
@@ -4212,7 +4238,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" s="36"/>
       <c r="B67" s="43"/>
       <c r="C67" s="10" t="s">
@@ -4226,7 +4252,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" s="36"/>
       <c r="B68" s="43"/>
       <c r="C68" s="10" t="s">
@@ -4240,7 +4266,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" s="36"/>
       <c r="B69" s="43"/>
       <c r="C69" s="10" t="s">
@@ -4254,7 +4280,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" s="36"/>
       <c r="B70" s="43"/>
       <c r="C70" s="10" t="s">
@@ -4268,7 +4294,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" s="36"/>
       <c r="B71" s="43"/>
       <c r="C71" s="10" t="s">
@@ -4282,7 +4308,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" s="36"/>
       <c r="B72" s="43"/>
       <c r="C72" s="10" t="s">
@@ -4296,7 +4322,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73" s="36"/>
       <c r="B73" s="43"/>
       <c r="C73" s="10" t="s">
@@ -4310,7 +4336,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74" s="36"/>
       <c r="B74" s="43"/>
       <c r="C74" s="10" t="s">
@@ -4324,7 +4350,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="75" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A75" s="37"/>
       <c r="B75" s="44"/>
       <c r="C75" s="22"/>
@@ -4332,7 +4358,7 @@
       <c r="E75" s="23"/>
       <c r="F75" s="22"/>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76" s="35" t="s">
         <v>72</v>
       </c>
@@ -4350,7 +4376,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A77" s="36"/>
       <c r="B77" s="43"/>
       <c r="C77" s="10" t="s">
@@ -4364,12 +4390,12 @@
         <v>149</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78" s="36"/>
       <c r="B78" s="47"/>
       <c r="E78" s="13"/>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A79" s="36"/>
       <c r="B79" s="41" t="s">
         <v>4</v>
@@ -4385,7 +4411,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A80" s="36"/>
       <c r="B80" s="39"/>
       <c r="C80" s="10" t="s">
@@ -4399,7 +4425,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A81" s="36"/>
       <c r="B81" s="39"/>
       <c r="C81" s="10" t="s">
@@ -4413,7 +4439,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A82" s="36"/>
       <c r="B82" s="39"/>
       <c r="C82" s="10" t="s">
@@ -4427,7 +4453,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A83" s="36"/>
       <c r="B83" s="39"/>
       <c r="C83" s="10" t="s">
@@ -4441,7 +4467,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A84" s="36"/>
       <c r="B84" s="39"/>
       <c r="C84" s="10" t="s">
@@ -4455,7 +4481,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A85" s="36"/>
       <c r="B85" s="39"/>
       <c r="C85" s="10" t="s">
@@ -4469,7 +4495,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A86" s="36"/>
       <c r="B86" s="39"/>
       <c r="C86" s="10" t="s">
@@ -4483,7 +4509,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A87" s="36"/>
       <c r="B87" s="39"/>
       <c r="C87" s="10" t="s">
@@ -4497,11 +4523,11 @@
         <v>149</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A88" s="36"/>
       <c r="B88" s="40"/>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A89" s="36"/>
       <c r="B89" s="41" t="s">
         <v>5</v>
@@ -4517,7 +4543,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A90" s="36"/>
       <c r="B90" s="39"/>
       <c r="C90" s="10" t="s">
@@ -4531,7 +4557,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A91" s="36"/>
       <c r="B91" s="39"/>
       <c r="C91" s="10" t="s">
@@ -4545,7 +4571,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A92" s="36"/>
       <c r="B92" s="39"/>
       <c r="C92" s="10" t="s">
@@ -4559,7 +4585,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A93" s="36"/>
       <c r="B93" s="39"/>
       <c r="C93" s="10" t="s">
@@ -4573,7 +4599,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A94" s="36"/>
       <c r="B94" s="39"/>
       <c r="C94" s="10" t="s">
@@ -4587,7 +4613,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A95" s="36"/>
       <c r="B95" s="39"/>
       <c r="C95" s="10" t="s">
@@ -4601,7 +4627,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A96" s="36"/>
       <c r="B96" s="39"/>
       <c r="C96" s="10" t="s">
@@ -4615,7 +4641,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A97" s="36"/>
       <c r="B97" s="39"/>
       <c r="C97" s="10" t="s">
@@ -4629,11 +4655,11 @@
         <v>149</v>
       </c>
     </row>
-    <row r="98" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A98" s="37"/>
       <c r="B98" s="42"/>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A99" s="35" t="s">
         <v>76</v>
       </c>
@@ -4651,7 +4677,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A100" s="36"/>
       <c r="B100" s="43"/>
       <c r="C100" s="10" t="s">
@@ -4665,7 +4691,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A101" s="36"/>
       <c r="B101" s="47"/>
       <c r="C101" s="18"/>
@@ -4673,7 +4699,7 @@
       <c r="E101" s="19"/>
       <c r="F101" s="18"/>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A102" s="36"/>
       <c r="B102" s="46" t="s">
         <v>326</v>
@@ -4689,7 +4715,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A103" s="36"/>
       <c r="B103" s="43"/>
       <c r="C103" s="10" t="s">
@@ -4703,12 +4729,12 @@
         <v>149</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A104" s="36"/>
       <c r="B104" s="47"/>
       <c r="E104" s="15"/>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A105" s="36"/>
       <c r="B105" s="46" t="s">
         <v>79</v>
@@ -4724,7 +4750,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A106" s="36"/>
       <c r="B106" s="43"/>
       <c r="C106" s="10" t="s">
@@ -4738,7 +4764,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A107" s="36"/>
       <c r="B107" s="47"/>
       <c r="C107" s="18"/>
@@ -4746,7 +4772,7 @@
       <c r="E107" s="19"/>
       <c r="F107" s="18"/>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A108" s="36"/>
       <c r="B108" s="46" t="s">
         <v>272</v>
@@ -4762,7 +4788,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A109" s="36"/>
       <c r="B109" s="43"/>
       <c r="C109" s="10" t="s">
@@ -4776,7 +4802,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="110" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A110" s="37"/>
       <c r="B110" s="44"/>
       <c r="C110" s="22"/>
@@ -4784,7 +4810,7 @@
       <c r="E110" s="23"/>
       <c r="F110" s="22"/>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A111" s="35" t="s">
         <v>163</v>
       </c>
@@ -4802,7 +4828,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A112" s="36"/>
       <c r="B112" s="43"/>
       <c r="C112" s="10" t="s">
@@ -4815,7 +4841,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A113" s="36"/>
       <c r="B113" s="47"/>
       <c r="C113" s="18"/>
@@ -4823,7 +4849,7 @@
       <c r="E113" s="18"/>
       <c r="F113" s="18"/>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A114" s="36"/>
       <c r="B114" s="46" t="s">
         <v>183</v>
@@ -4838,7 +4864,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A115" s="36"/>
       <c r="B115" s="43"/>
       <c r="C115" s="10" t="s">
@@ -4851,7 +4877,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A116" s="36"/>
       <c r="B116" s="43"/>
       <c r="C116" s="10" t="s">
@@ -4864,7 +4890,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A117" s="36"/>
       <c r="B117" s="43"/>
       <c r="C117" s="10" t="s">
@@ -4877,7 +4903,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A118" s="36"/>
       <c r="B118" s="43"/>
       <c r="C118" s="10" t="s">
@@ -4890,7 +4916,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A119" s="36"/>
       <c r="B119" s="43"/>
       <c r="C119" s="10" t="s">
@@ -4903,11 +4929,11 @@
         <v>149</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A120" s="36"/>
       <c r="B120" s="43"/>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A121" s="36"/>
       <c r="B121" s="46" t="s">
         <v>206</v>
@@ -4923,7 +4949,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A122" s="36"/>
       <c r="B122" s="43"/>
       <c r="C122" s="10" t="s">
@@ -4936,7 +4962,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A123" s="36"/>
       <c r="B123" s="43"/>
       <c r="C123" s="10" t="s">
@@ -4949,7 +4975,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A124" s="36"/>
       <c r="B124" s="43"/>
       <c r="C124" s="10" t="s">
@@ -4962,7 +4988,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A125" s="36"/>
       <c r="B125" s="43"/>
       <c r="C125" s="10" t="s">
@@ -4975,7 +5001,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A126" s="36"/>
       <c r="B126" s="43"/>
       <c r="C126" s="10" t="s">
@@ -4988,7 +5014,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A127" s="36"/>
       <c r="B127" s="43"/>
       <c r="C127" s="10" t="s">
@@ -5001,7 +5027,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A128" s="36"/>
       <c r="B128" s="43"/>
       <c r="C128" s="10" t="s">
@@ -5014,7 +5040,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A129" s="36"/>
       <c r="B129" s="43"/>
       <c r="C129" s="10" t="s">
@@ -5027,7 +5053,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A130" s="36"/>
       <c r="B130" s="43"/>
       <c r="C130" s="10" t="s">
@@ -5040,7 +5066,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A131" s="36"/>
       <c r="B131" s="43"/>
       <c r="C131" s="10" t="s">
@@ -5053,7 +5079,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A132" s="36"/>
       <c r="B132" s="43"/>
       <c r="C132" s="10" t="s">
@@ -5066,11 +5092,11 @@
         <v>213</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A133" s="36"/>
       <c r="B133" s="43"/>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A134" s="36"/>
       <c r="B134" s="46" t="s">
         <v>222</v>
@@ -5086,7 +5112,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A135" s="36"/>
       <c r="B135" s="43"/>
       <c r="C135" s="10" t="s">
@@ -5099,7 +5125,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A136" s="36"/>
       <c r="B136" s="43"/>
       <c r="C136" s="10" t="s">
@@ -5112,7 +5138,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A137" s="36"/>
       <c r="B137" s="43"/>
       <c r="C137" s="10" t="s">
@@ -5125,7 +5151,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A138" s="36"/>
       <c r="B138" s="43"/>
       <c r="C138" s="10" t="s">
@@ -5138,11 +5164,11 @@
         <v>213</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A139" s="36"/>
       <c r="B139" s="47"/>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A140" s="36"/>
       <c r="B140" s="46" t="s">
         <v>363</v>
@@ -5158,7 +5184,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A141" s="36"/>
       <c r="B141" s="43"/>
       <c r="C141" s="10" t="s">
@@ -5171,20 +5197,11 @@
         <v>295</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A142" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="A2:A43"/>
-    <mergeCell ref="B2:B11"/>
-    <mergeCell ref="B12:B22"/>
-    <mergeCell ref="B33:B43"/>
-    <mergeCell ref="A44:A75"/>
-    <mergeCell ref="B64:B75"/>
-    <mergeCell ref="B23:B32"/>
-    <mergeCell ref="B44:B53"/>
-    <mergeCell ref="B54:B63"/>
     <mergeCell ref="B140:B141"/>
     <mergeCell ref="B134:B139"/>
     <mergeCell ref="A111:A142"/>
@@ -5200,6 +5217,15 @@
     <mergeCell ref="B105:B107"/>
     <mergeCell ref="B99:B101"/>
     <mergeCell ref="B102:B104"/>
+    <mergeCell ref="A2:A43"/>
+    <mergeCell ref="B2:B11"/>
+    <mergeCell ref="B12:B22"/>
+    <mergeCell ref="B33:B43"/>
+    <mergeCell ref="A44:A75"/>
+    <mergeCell ref="B64:B75"/>
+    <mergeCell ref="B23:B32"/>
+    <mergeCell ref="B44:B53"/>
+    <mergeCell ref="B54:B63"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -5209,57 +5235,57 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93C614C4-2B7C-4798-B4E2-788104541F45}">
   <dimension ref="B1:B31"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="11.5546875" style="3"/>
+    <col min="2" max="2" width="11.54296875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B1" s="3" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B2" s="3" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="22" spans="2:2" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:2" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B22" s="6" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B24" s="3" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B26" s="3" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B27" s="3" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B28" s="3" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B29" s="4" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B30" s="5" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B31" s="5"/>
     </row>
   </sheetData>
